--- a/docs/examples/test-armaturenstaat-woning.xlsx
+++ b/docs/examples/test-armaturenstaat-woning.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Armaturenstaat" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Delta Light" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Wever en Ducre" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="87">
   <si>
     <t>Project:</t>
   </si>
@@ -269,6 +270,9 @@
   </si>
   <si>
     <t>Aantallen</t>
+  </si>
+  <si>
+    <t>Wever en Ducre trimless 1.0 18486LQ3</t>
   </si>
 </sst>
 </file>
@@ -1282,4 +1286,645 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L102"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="G16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="G20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>48</v>
+      </c>
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>49</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="G49" t="s">
+        <v>50</v>
+      </c>
+      <c r="I49" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="G52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>54</v>
+      </c>
+      <c r="I55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>56</v>
+      </c>
+      <c r="I56" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="G57" t="s">
+        <v>56</v>
+      </c>
+      <c r="I57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="G61" t="s">
+        <v>60</v>
+      </c>
+      <c r="I61" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="G65" t="s">
+        <v>63</v>
+      </c>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="s">
+        <v>66</v>
+      </c>
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="G73" t="s">
+        <v>66</v>
+      </c>
+      <c r="I73" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>39</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>40</v>
+      </c>
+      <c r="I76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>67</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="G79" t="s">
+        <v>68</v>
+      </c>
+      <c r="I79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
+      </c>
+      <c r="G82" t="s">
+        <v>70</v>
+      </c>
+      <c r="I82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>70</v>
+      </c>
+      <c r="I83" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>71</v>
+      </c>
+      <c r="E86">
+        <v>4</v>
+      </c>
+      <c r="G86" t="s">
+        <v>72</v>
+      </c>
+      <c r="I86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>73</v>
+      </c>
+      <c r="I87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E88">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>74</v>
+      </c>
+      <c r="I88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="G91" t="s">
+        <v>76</v>
+      </c>
+      <c r="I91" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>78</v>
+      </c>
+      <c r="I93" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>80</v>
+      </c>
+      <c r="C97" t="s">
+        <v>81</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="I97" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" t="s">
+        <v>84</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="I99" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>85</v>
+      </c>
+      <c r="E102">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>